--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0005.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0005.xlsx
@@ -19879,7 +19879,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>An error occurred Vui lòng liên hệ Bộ phận Chăm sóc Khách hàng để được hỗ trợ</t>
+          <t>Đã xảy ra lỗi. Vui lòng liên hệ Bộ phận Chăm sóc Khách hàng để được hỗ trợ.</t>
         </is>
       </c>
     </row>
@@ -19944,7 +19944,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>An error occurred Vui lòng liên hệ Bộ phận Chăm sóc Khách hàng để được hỗ trợ</t>
+          <t>Đã xảy ra lỗi. Vui lòng liên hệ Bộ phận Chăm sóc Khách hàng để được hỗ trợ.</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Ngày Ra Khơi, Thuyền Trưởng!</t>
+          <t>Ngày Hành Trình, Thuyền trưởng!</t>
         </is>
       </c>
     </row>
@@ -23584,7 +23584,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Ta luôn có thể bắt đầu lại mà. Iuno, lần này đừng quên ta nhé.</t>
+          <t>Ta luôn có thể bắt đầu lại mà. Iuno, lần này đừng quên tao nhé.</t>
         </is>
       </c>
     </row>
@@ -24429,7 +24429,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Cái gì không giết được ta thì cứ liên tục đánh ta. Hết lần này đến lần khác.</t>
+          <t>Cái gì không giết được tao thì cứ liên tục đánh tao. Hết lần này đến lần khác.</t>
         </is>
       </c>
     </row>
@@ -25607,7 +25607,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Remaining: {0}</t>
+          <t>Còn lại: {0}</t>
         </is>
       </c>
     </row>
@@ -25737,7 +25737,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Hoàn thành cả hai thử thách "Khu Vực Ổn Định" và "Khu Vực Thí Nghiệm" tại Tháp Nghịch Cảnh để nhận Cộng Hưởng Giả Yuanwu cùng các phần thưởng khác.</t>
+          <t>Hoàn thành cả hai thử thách "Khu Vực Ổn Định" và "Khu Vực Thí Nghiệm" tại Tháp Nghịch Cảnh để nhận Resonator Yuanwu cùng các phần thưởng khác.</t>
         </is>
       </c>
     </row>
@@ -25932,7 +25932,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Completed: {0}/{1}</t>
+          <t>Hoàn thành: {0}/{1}</t>
         </is>
       </c>
     </row>
@@ -25997,7 +25997,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>&lt;color=#fde7a1&gt;{0}&lt;/color&gt;/{1}</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
     </row>
@@ -27947,7 +27947,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Dừng thời gian để người dùng ghi lại những khoảnh khắc đỉnh cao của Cộng Hưởng Giả trong chiến đấu từ nhiều góc độ khác nhau.</t>
+          <t>Dừng thời gian để người dùng ghi lại những khoảnh khắc đỉnh cao của Resonator trong chiến đấu từ nhiều góc độ khác nhau.</t>
         </is>
       </c>
     </row>
@@ -29247,7 +29247,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Bạn không thể đổi Cộng Hưởng Giả trong trận chiến.</t>
+          <t>Bạn không thể đổi Resonator trong trận chiến.</t>
         </is>
       </c>
     </row>
@@ -29312,7 +29312,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Bây giờ bạn không thể đổi Cộng Hưởng Giả.</t>
+          <t>Bây giờ bạn không thể đổi Resonator.</t>
         </is>
       </c>
     </row>
@@ -32172,7 +32172,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Tăng 50% Tái Tạo Năng Lượng cho tất cả Cộng Hưởng Giả trong đội trong 3 giờ. Chỉ có hiệu lực với Cộng Hưởng Giả của bạn trong Chế Độ Hợp Tác.</t>
+          <t>Tăng 50% Tái Tạo Năng Lượng cho tất cả Resonator trong đội trong 3 giờ. Chỉ có hiệu lực với Resonator của bạn trong Chế Độ Hợp Tác.</t>
         </is>
       </c>
     </row>
